--- a/polls/025_simple_voting_form_template--polls.xlsx
+++ b/polls/025_simple_voting_form_template--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_control</t>
+          <t>form_category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>simple-voting-form-template</t>
+          <t>Select a category for your vote</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vote_category</t>
+          <t>form_question</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>select-category</t>
+          <t>Select a question to answer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vote_question</t>
+          <t>form_choice_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>select-question</t>
+          <t>Select choice 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vote_choice_1</t>
+          <t>form_choice_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>select-choice-1</t>
+          <t>Select choice 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vote_choice_2</t>
+          <t>form_choice_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>select-choice-2</t>
+          <t>Select choice 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_choice_3</t>
+          <t>form_confirm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>select-choice-3</t>
+          <t>Confirm your choice</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_choice_4</t>
+          <t>form_note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>select-choice-4</t>
+          <t>Add a note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_controls</t>
+          <t>form_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>form-controls</t>
+          <t>Select time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_controls</t>
+          <t>form_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form-controls</t>
+          <t>Enter email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_controls</t>
+          <t>form_text</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form-controls</t>
+          <t>Enter text</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_controls</t>
+          <t>form_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>form-controls</t>
+          <t>Enter number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,62 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_controls</t>
+          <t>form_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>form-controls</t>
+          <t>Select date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_controls</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>form-controls</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_controls</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>form-controls</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -873,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vote_category_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -890,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vote_category_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -907,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vote_category_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -924,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vote_question_choices</t>
+          <t>form_question_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -941,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vote_question_choices</t>
+          <t>form_question_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vote_question_choices</t>
+          <t>form_question_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -975,109 +929,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vote_choice_1_choices</t>
+          <t>form_choice_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vote_choice_1_choices</t>
+          <t>form_choice_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vote_choice_1_choices</t>
+          <t>form_choice_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vote_choice_2_choices</t>
+          <t>form_choice_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vote_choice_2_choices</t>
+          <t>form_choice_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vote_choice_2_choices</t>
+          <t>form_choice_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_choice_3_choices</t>
+          <t>form_choice_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1094,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_choice_3_choices</t>
+          <t>form_choice_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1111,102 +1065,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_choice_4_choices</t>
+          <t>form_confirm_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_choice_4_choices</t>
+          <t>form_confirm_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>form_controls_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_controls_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_controls_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_controls_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
